--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271908</v>
+        <v>121271898</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>94494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317825</v>
+        <v>317861</v>
       </c>
       <c r="R2" t="n">
-        <v>6518651</v>
+        <v>6518583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271901</v>
+        <v>121271908</v>
       </c>
       <c r="B3" t="n">
-        <v>96338</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317856</v>
+        <v>317825</v>
       </c>
       <c r="R3" t="n">
-        <v>6518587</v>
+        <v>6518651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271912</v>
+        <v>121271903</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>96348</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317641</v>
+        <v>317791</v>
       </c>
       <c r="R4" t="n">
-        <v>6518340</v>
+        <v>6518574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +989,7 @@
         <v>121271910</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271903</v>
+        <v>121271911</v>
       </c>
       <c r="B6" t="n">
-        <v>96338</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317791</v>
+        <v>317812</v>
       </c>
       <c r="R6" t="n">
-        <v>6518574</v>
+        <v>6518465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271898</v>
+        <v>121271904</v>
       </c>
       <c r="B7" t="n">
-        <v>94484</v>
+        <v>96348</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317861</v>
+        <v>317846</v>
       </c>
       <c r="R7" t="n">
-        <v>6518583</v>
+        <v>6518607</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271904</v>
+        <v>121271901</v>
       </c>
       <c r="B8" t="n">
-        <v>96338</v>
+        <v>96348</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317846</v>
+        <v>317856</v>
       </c>
       <c r="R8" t="n">
-        <v>6518607</v>
+        <v>6518587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,7 +1412,7 @@
         <v>121271909</v>
       </c>
       <c r="B9" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271911</v>
+        <v>121271912</v>
       </c>
       <c r="B10" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317812</v>
+        <v>317641</v>
       </c>
       <c r="R10" t="n">
-        <v>6518465</v>
+        <v>6518340</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
         <v>121271900</v>
       </c>
       <c r="B11" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271898</v>
+        <v>121271910</v>
       </c>
       <c r="B2" t="n">
-        <v>94494</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317861</v>
+        <v>317862</v>
       </c>
       <c r="R2" t="n">
-        <v>6518583</v>
+        <v>6518585</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271908</v>
+        <v>121271911</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317825</v>
+        <v>317812</v>
       </c>
       <c r="R3" t="n">
-        <v>6518651</v>
+        <v>6518465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack på granlåga</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271910</v>
+        <v>121271908</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317862</v>
+        <v>317825</v>
       </c>
       <c r="R5" t="n">
-        <v>6518585</v>
+        <v>6518651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271911</v>
+        <v>121271901</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>96348</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317812</v>
+        <v>317856</v>
       </c>
       <c r="R6" t="n">
-        <v>6518465</v>
+        <v>6518587</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271901</v>
+        <v>121271909</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317856</v>
+        <v>317812</v>
       </c>
       <c r="R8" t="n">
-        <v>6518587</v>
+        <v>6518650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271909</v>
+        <v>121271898</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>94494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317812</v>
+        <v>317861</v>
       </c>
       <c r="R9" t="n">
-        <v>6518650</v>
+        <v>6518583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271910</v>
+        <v>121271911</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317862</v>
+        <v>317812</v>
       </c>
       <c r="R2" t="n">
-        <v>6518585</v>
+        <v>6518465</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271911</v>
+        <v>121271901</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>96361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317812</v>
+        <v>317856</v>
       </c>
       <c r="R3" t="n">
-        <v>6518465</v>
+        <v>6518587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>121271903</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
+        <v>96361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271908</v>
+        <v>121271898</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>94506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317825</v>
+        <v>317861</v>
       </c>
       <c r="R5" t="n">
-        <v>6518651</v>
+        <v>6518583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271901</v>
+        <v>121271912</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317856</v>
+        <v>317641</v>
       </c>
       <c r="R6" t="n">
-        <v>6518587</v>
+        <v>6518340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271904</v>
+        <v>121271909</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317846</v>
+        <v>317812</v>
       </c>
       <c r="R7" t="n">
-        <v>6518607</v>
+        <v>6518650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271909</v>
+        <v>121271908</v>
       </c>
       <c r="B8" t="n">
         <v>57367</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317812</v>
+        <v>317825</v>
       </c>
       <c r="R8" t="n">
-        <v>6518650</v>
+        <v>6518651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271898</v>
+        <v>121271904</v>
       </c>
       <c r="B9" t="n">
-        <v>94494</v>
+        <v>96361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317861</v>
+        <v>317846</v>
       </c>
       <c r="R9" t="n">
-        <v>6518583</v>
+        <v>6518607</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271912</v>
+        <v>121271910</v>
       </c>
       <c r="B10" t="n">
         <v>57367</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317641</v>
+        <v>317862</v>
       </c>
       <c r="R10" t="n">
-        <v>6518340</v>
+        <v>6518585</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271911</v>
+        <v>121271912</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317812</v>
+        <v>317641</v>
       </c>
       <c r="R2" t="n">
-        <v>6518465</v>
+        <v>6518340</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271901</v>
+        <v>121271904</v>
       </c>
       <c r="B3" t="n">
-        <v>96361</v>
+        <v>96362</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317856</v>
+        <v>317846</v>
       </c>
       <c r="R3" t="n">
-        <v>6518587</v>
+        <v>6518607</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +887,7 @@
         <v>121271903</v>
       </c>
       <c r="B4" t="n">
-        <v>96361</v>
+        <v>96362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271898</v>
+        <v>121271901</v>
       </c>
       <c r="B5" t="n">
-        <v>94506</v>
+        <v>96362</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317861</v>
+        <v>317856</v>
       </c>
       <c r="R5" t="n">
-        <v>6518583</v>
+        <v>6518587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271912</v>
+        <v>121271898</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>94507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317641</v>
+        <v>317861</v>
       </c>
       <c r="R6" t="n">
-        <v>6518340</v>
+        <v>6518583</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271909</v>
+        <v>121271911</v>
       </c>
       <c r="B7" t="n">
         <v>57367</v>
@@ -1243,7 +1238,7 @@
         <v>317812</v>
       </c>
       <c r="R7" t="n">
-        <v>6518650</v>
+        <v>6518465</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271908</v>
+        <v>121271909</v>
       </c>
       <c r="B8" t="n">
         <v>57367</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317825</v>
+        <v>317812</v>
       </c>
       <c r="R8" t="n">
-        <v>6518651</v>
+        <v>6518650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack på granlåga</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271904</v>
+        <v>121271908</v>
       </c>
       <c r="B9" t="n">
-        <v>96361</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317846</v>
+        <v>317825</v>
       </c>
       <c r="R9" t="n">
-        <v>6518607</v>
+        <v>6518651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271912</v>
+        <v>121271898</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>94510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317641</v>
+        <v>317861</v>
       </c>
       <c r="R2" t="n">
-        <v>6518340</v>
+        <v>6518583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271904</v>
+        <v>121271911</v>
       </c>
       <c r="B3" t="n">
-        <v>96362</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317846</v>
+        <v>317812</v>
       </c>
       <c r="R3" t="n">
-        <v>6518607</v>
+        <v>6518465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271903</v>
+        <v>121271908</v>
       </c>
       <c r="B4" t="n">
-        <v>96362</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317791</v>
+        <v>317825</v>
       </c>
       <c r="R4" t="n">
-        <v>6518574</v>
+        <v>6518651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271901</v>
+        <v>121271903</v>
       </c>
       <c r="B5" t="n">
-        <v>96362</v>
+        <v>96365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317856</v>
+        <v>317791</v>
       </c>
       <c r="R5" t="n">
-        <v>6518587</v>
+        <v>6518574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271898</v>
+        <v>121271912</v>
       </c>
       <c r="B6" t="n">
-        <v>94507</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317861</v>
+        <v>317641</v>
       </c>
       <c r="R6" t="n">
-        <v>6518583</v>
+        <v>6518340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271911</v>
+        <v>121271909</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,7 +1243,7 @@
         <v>317812</v>
       </c>
       <c r="R7" t="n">
-        <v>6518465</v>
+        <v>6518650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271909</v>
+        <v>121271910</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317812</v>
+        <v>317862</v>
       </c>
       <c r="R8" t="n">
-        <v>6518650</v>
+        <v>6518585</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271908</v>
+        <v>121271901</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>96365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317825</v>
+        <v>317856</v>
       </c>
       <c r="R9" t="n">
-        <v>6518651</v>
+        <v>6518587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosökshack på granlåga</t>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271910</v>
+        <v>121271904</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>96365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317862</v>
+        <v>317846</v>
       </c>
       <c r="R10" t="n">
-        <v>6518585</v>
+        <v>6518607</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
         <v>121271900</v>
       </c>
       <c r="B11" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271911</v>
+        <v>121271909</v>
       </c>
       <c r="B3" t="n">
         <v>57370</v>
@@ -820,7 +820,7 @@
         <v>317812</v>
       </c>
       <c r="R3" t="n">
-        <v>6518465</v>
+        <v>6518650</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271908</v>
+        <v>121271903</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>96365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317825</v>
+        <v>317791</v>
       </c>
       <c r="R4" t="n">
-        <v>6518651</v>
+        <v>6518574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271903</v>
+        <v>121271911</v>
       </c>
       <c r="B5" t="n">
-        <v>96365</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317791</v>
+        <v>317812</v>
       </c>
       <c r="R5" t="n">
-        <v>6518574</v>
+        <v>6518465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271912</v>
+        <v>121271904</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>96365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317641</v>
+        <v>317846</v>
       </c>
       <c r="R6" t="n">
-        <v>6518340</v>
+        <v>6518607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271909</v>
+        <v>121271912</v>
       </c>
       <c r="B7" t="n">
         <v>57370</v>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317812</v>
+        <v>317641</v>
       </c>
       <c r="R7" t="n">
-        <v>6518650</v>
+        <v>6518340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271904</v>
+        <v>121271908</v>
       </c>
       <c r="B10" t="n">
-        <v>96365</v>
+        <v>57370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317846</v>
+        <v>317825</v>
       </c>
       <c r="R10" t="n">
-        <v>6518607</v>
+        <v>6518651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271898</v>
+        <v>121271901</v>
       </c>
       <c r="B2" t="n">
-        <v>94510</v>
+        <v>96371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317861</v>
+        <v>317856</v>
       </c>
       <c r="R2" t="n">
-        <v>6518583</v>
+        <v>6518587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271909</v>
+        <v>121271912</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317812</v>
+        <v>317641</v>
       </c>
       <c r="R3" t="n">
-        <v>6518650</v>
+        <v>6518340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +892,7 @@
         <v>121271903</v>
       </c>
       <c r="B4" t="n">
-        <v>96365</v>
+        <v>96371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271911</v>
+        <v>121271908</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317812</v>
+        <v>317825</v>
       </c>
       <c r="R5" t="n">
-        <v>6518465</v>
+        <v>6518651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1101,7 @@
         <v>121271904</v>
       </c>
       <c r="B6" t="n">
-        <v>96365</v>
+        <v>96371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271912</v>
+        <v>121271898</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>94516</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317641</v>
+        <v>317861</v>
       </c>
       <c r="R7" t="n">
-        <v>6518340</v>
+        <v>6518583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271910</v>
+        <v>121271911</v>
       </c>
       <c r="B8" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317862</v>
+        <v>317812</v>
       </c>
       <c r="R8" t="n">
-        <v>6518585</v>
+        <v>6518465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271901</v>
+        <v>121271909</v>
       </c>
       <c r="B9" t="n">
-        <v>96365</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317856</v>
+        <v>317812</v>
       </c>
       <c r="R9" t="n">
-        <v>6518587</v>
+        <v>6518650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271908</v>
+        <v>121271910</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317825</v>
+        <v>317862</v>
       </c>
       <c r="R10" t="n">
-        <v>6518651</v>
+        <v>6518585</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födosökshack på granlåga</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
         <v>121271900</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271901</v>
+        <v>121271912</v>
       </c>
       <c r="B2" t="n">
-        <v>96371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317856</v>
+        <v>317641</v>
       </c>
       <c r="R2" t="n">
-        <v>6518587</v>
+        <v>6518340</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271912</v>
+        <v>121271911</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317641</v>
+        <v>317812</v>
       </c>
       <c r="R3" t="n">
-        <v>6518340</v>
+        <v>6518465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271903</v>
+        <v>121271898</v>
       </c>
       <c r="B4" t="n">
-        <v>96371</v>
+        <v>94517</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317791</v>
+        <v>317861</v>
       </c>
       <c r="R4" t="n">
-        <v>6518574</v>
+        <v>6518583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271908</v>
+        <v>121271904</v>
       </c>
       <c r="B5" t="n">
-        <v>57371</v>
+        <v>96372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317825</v>
+        <v>317846</v>
       </c>
       <c r="R5" t="n">
-        <v>6518651</v>
+        <v>6518607</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271904</v>
+        <v>121271909</v>
       </c>
       <c r="B6" t="n">
-        <v>96371</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317846</v>
+        <v>317812</v>
       </c>
       <c r="R6" t="n">
-        <v>6518607</v>
+        <v>6518650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271898</v>
+        <v>121271910</v>
       </c>
       <c r="B7" t="n">
-        <v>94516</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317861</v>
+        <v>317862</v>
       </c>
       <c r="R7" t="n">
-        <v>6518583</v>
+        <v>6518585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271911</v>
+        <v>121271908</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317812</v>
+        <v>317825</v>
       </c>
       <c r="R8" t="n">
-        <v>6518465</v>
+        <v>6518651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271909</v>
+        <v>121271901</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>96372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317812</v>
+        <v>317856</v>
       </c>
       <c r="R9" t="n">
-        <v>6518650</v>
+        <v>6518587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271910</v>
+        <v>121271903</v>
       </c>
       <c r="B10" t="n">
-        <v>57371</v>
+        <v>96372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317862</v>
+        <v>317791</v>
       </c>
       <c r="R10" t="n">
-        <v>6518585</v>
+        <v>6518574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
         <v>121271900</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271912</v>
+        <v>121271909</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317641</v>
+        <v>317812</v>
       </c>
       <c r="R2" t="n">
-        <v>6518340</v>
+        <v>6518650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271911</v>
+        <v>121271901</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317812</v>
+        <v>317856</v>
       </c>
       <c r="R3" t="n">
-        <v>6518465</v>
+        <v>6518587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271898</v>
+        <v>121271910</v>
       </c>
       <c r="B4" t="n">
-        <v>94517</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317861</v>
+        <v>317862</v>
       </c>
       <c r="R4" t="n">
-        <v>6518583</v>
+        <v>6518585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271904</v>
+        <v>121271898</v>
       </c>
       <c r="B5" t="n">
-        <v>96372</v>
+        <v>94517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317846</v>
+        <v>317861</v>
       </c>
       <c r="R5" t="n">
-        <v>6518607</v>
+        <v>6518583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271909</v>
+        <v>121271903</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317812</v>
+        <v>317791</v>
       </c>
       <c r="R6" t="n">
-        <v>6518650</v>
+        <v>6518574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271910</v>
+        <v>121271904</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317862</v>
+        <v>317846</v>
       </c>
       <c r="R7" t="n">
-        <v>6518585</v>
+        <v>6518607</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271908</v>
+        <v>121271912</v>
       </c>
       <c r="B8" t="n">
         <v>57372</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317825</v>
+        <v>317641</v>
       </c>
       <c r="R8" t="n">
-        <v>6518651</v>
+        <v>6518340</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack på granlåga</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271901</v>
+        <v>121271908</v>
       </c>
       <c r="B9" t="n">
-        <v>96372</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317856</v>
+        <v>317825</v>
       </c>
       <c r="R9" t="n">
-        <v>6518587</v>
+        <v>6518651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271903</v>
+        <v>121271911</v>
       </c>
       <c r="B10" t="n">
-        <v>96372</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317791</v>
+        <v>317812</v>
       </c>
       <c r="R10" t="n">
-        <v>6518574</v>
+        <v>6518465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271909</v>
+        <v>121271904</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317812</v>
+        <v>317846</v>
       </c>
       <c r="R2" t="n">
-        <v>6518650</v>
+        <v>6518607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271901</v>
+        <v>121271912</v>
       </c>
       <c r="B3" t="n">
-        <v>96372</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317856</v>
+        <v>317641</v>
       </c>
       <c r="R3" t="n">
-        <v>6518587</v>
+        <v>6518340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271910</v>
+        <v>121271908</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317862</v>
+        <v>317825</v>
       </c>
       <c r="R4" t="n">
-        <v>6518585</v>
+        <v>6518651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271903</v>
+        <v>121271909</v>
       </c>
       <c r="B6" t="n">
-        <v>96372</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317791</v>
+        <v>317812</v>
       </c>
       <c r="R6" t="n">
-        <v>6518574</v>
+        <v>6518650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271904</v>
+        <v>121271901</v>
       </c>
       <c r="B7" t="n">
         <v>96372</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317846</v>
+        <v>317856</v>
       </c>
       <c r="R7" t="n">
-        <v>6518607</v>
+        <v>6518587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271912</v>
+        <v>121271911</v>
       </c>
       <c r="B8" t="n">
         <v>57372</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317641</v>
+        <v>317812</v>
       </c>
       <c r="R8" t="n">
-        <v>6518340</v>
+        <v>6518465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271908</v>
+        <v>121271903</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317825</v>
+        <v>317791</v>
       </c>
       <c r="R9" t="n">
-        <v>6518651</v>
+        <v>6518574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271911</v>
+        <v>121271910</v>
       </c>
       <c r="B10" t="n">
         <v>57372</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317812</v>
+        <v>317862</v>
       </c>
       <c r="R10" t="n">
-        <v>6518465</v>
+        <v>6518585</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 51899-2024 artfynd.xlsx
+++ b/artfynd/A 51899-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121271904</v>
+        <v>121271898</v>
       </c>
       <c r="B2" t="n">
-        <v>96372</v>
+        <v>94517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317846</v>
+        <v>317861</v>
       </c>
       <c r="R2" t="n">
-        <v>6518607</v>
+        <v>6518583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271912</v>
+        <v>121271903</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317641</v>
+        <v>317791</v>
       </c>
       <c r="R3" t="n">
-        <v>6518340</v>
+        <v>6518574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271908</v>
+        <v>121271912</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317825</v>
+        <v>317641</v>
       </c>
       <c r="R4" t="n">
-        <v>6518651</v>
+        <v>6518340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökshack på granlåga</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121271898</v>
+        <v>121271911</v>
       </c>
       <c r="B5" t="n">
-        <v>94517</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317861</v>
+        <v>317812</v>
       </c>
       <c r="R5" t="n">
-        <v>6518583</v>
+        <v>6518465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121271909</v>
+        <v>121271901</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317812</v>
+        <v>317856</v>
       </c>
       <c r="R6" t="n">
-        <v>6518650</v>
+        <v>6518587</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Förekommer spridd i detta parti</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121271901</v>
+        <v>121271910</v>
       </c>
       <c r="B7" t="n">
-        <v>96372</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317856</v>
+        <v>317862</v>
       </c>
       <c r="R7" t="n">
-        <v>6518587</v>
+        <v>6518585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Förekommer spridd i detta parti</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121271911</v>
+        <v>121271909</v>
       </c>
       <c r="B8" t="n">
         <v>57372</v>
@@ -1350,7 +1350,7 @@
         <v>317812</v>
       </c>
       <c r="R8" t="n">
-        <v>6518465</v>
+        <v>6518650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121271903</v>
+        <v>121271908</v>
       </c>
       <c r="B9" t="n">
-        <v>96372</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317791</v>
+        <v>317825</v>
       </c>
       <c r="R9" t="n">
-        <v>6518574</v>
+        <v>6518651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121271910</v>
+        <v>121271904</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>96372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317862</v>
+        <v>317846</v>
       </c>
       <c r="R10" t="n">
-        <v>6518585</v>
+        <v>6518607</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
